--- a/research/traditional_assets/database/data/switzerland/switzerland_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07580000000000001</v>
+        <v>0.0513</v>
       </c>
       <c r="E2">
-        <v>0.224</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="F2">
-        <v>0.225</v>
+        <v>0.141</v>
       </c>
       <c r="G2">
-        <v>0.0978128947563966</v>
+        <v>0.1958065444774974</v>
       </c>
       <c r="H2">
-        <v>0.0978128947563966</v>
+        <v>0.1958065444774974</v>
       </c>
       <c r="I2">
-        <v>0.1958344814328015</v>
+        <v>0.1705402263427871</v>
       </c>
       <c r="J2">
-        <v>0.1722515003802832</v>
+        <v>0.1404287532105374</v>
       </c>
       <c r="K2">
-        <v>8816</v>
+        <v>6142</v>
       </c>
       <c r="L2">
-        <v>0.2183637579570505</v>
+        <v>0.1473467037712312</v>
       </c>
       <c r="M2">
-        <v>5540</v>
+        <v>5097</v>
       </c>
       <c r="N2">
-        <v>0.06653327985050428</v>
+        <v>0.05566835335479101</v>
       </c>
       <c r="O2">
-        <v>0.6284029038112523</v>
+        <v>0.8298599804623901</v>
       </c>
       <c r="P2">
-        <v>1409</v>
+        <v>1375</v>
       </c>
       <c r="Q2">
-        <v>0.01692155077786291</v>
+        <v>0.01501745847809253</v>
       </c>
       <c r="R2">
-        <v>0.1598230490018149</v>
+        <v>0.223868446760013</v>
       </c>
       <c r="S2">
-        <v>4131</v>
+        <v>3722</v>
       </c>
       <c r="T2">
-        <v>0.7456678700361011</v>
+        <v>0.730233470669021</v>
       </c>
       <c r="U2">
-        <v>1620</v>
+        <v>2128</v>
       </c>
       <c r="V2">
-        <v>0.01945558002848681</v>
+        <v>0.0232415648300952</v>
       </c>
       <c r="W2">
-        <v>0.1562760356655381</v>
+        <v>0.1035436123942142</v>
       </c>
       <c r="X2">
-        <v>0.05433302067786813</v>
+        <v>0.0872238263126045</v>
       </c>
       <c r="Y2">
-        <v>0.1019430149876699</v>
+        <v>0.01631978608160974</v>
       </c>
       <c r="Z2">
-        <v>0.6766968311948668</v>
+        <v>0.6760626680878448</v>
       </c>
       <c r="AA2">
-        <v>0.116562044475899</v>
+        <v>0.09493863757176541</v>
       </c>
       <c r="AB2">
-        <v>0.04831953781254059</v>
+        <v>0.07927818805515746</v>
       </c>
       <c r="AC2">
-        <v>0.06824250666335845</v>
+        <v>0.01566044951660794</v>
       </c>
       <c r="AD2">
-        <v>18905</v>
+        <v>19870</v>
       </c>
       <c r="AE2">
-        <v>507.8724055675146</v>
+        <v>441.0060256363095</v>
       </c>
       <c r="AF2">
-        <v>19412.87240556752</v>
+        <v>20311.00602563631</v>
       </c>
       <c r="AG2">
-        <v>17792.87240556752</v>
+        <v>18183.00602563631</v>
       </c>
       <c r="AH2">
-        <v>0.1890628374957924</v>
+        <v>0.1815572112157526</v>
       </c>
       <c r="AI2">
-        <v>0.2465725554972349</v>
+        <v>0.298911026114896</v>
       </c>
       <c r="AJ2">
-        <v>0.1760633811164373</v>
+        <v>0.1656870001600712</v>
       </c>
       <c r="AK2">
-        <v>0.2307440163818306</v>
+        <v>0.2762450907156249</v>
       </c>
       <c r="AL2">
-        <v>492</v>
+        <v>542</v>
       </c>
       <c r="AM2">
-        <v>492</v>
+        <v>542</v>
       </c>
       <c r="AN2">
-        <v>2.278534410027721</v>
+        <v>2.656772295761465</v>
       </c>
       <c r="AO2">
-        <v>15.97154471544715</v>
+        <v>13.01660516605166</v>
       </c>
       <c r="AP2">
-        <v>2.144494685496868</v>
+        <v>2.431208186339926</v>
       </c>
       <c r="AQ2">
-        <v>15.97154471544715</v>
+        <v>13.01660516605166</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07580000000000001</v>
+        <v>0.0513</v>
       </c>
       <c r="E3">
-        <v>0.224</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="F3">
-        <v>0.225</v>
+        <v>0.141</v>
       </c>
       <c r="G3">
-        <v>0.0978128947563966</v>
+        <v>0.1958065444774974</v>
       </c>
       <c r="H3">
-        <v>0.0978128947563966</v>
+        <v>0.1958065444774974</v>
       </c>
       <c r="I3">
-        <v>0.1958344814328015</v>
+        <v>0.1705402263427871</v>
       </c>
       <c r="J3">
-        <v>0.1722515003802832</v>
+        <v>0.1404287532105374</v>
       </c>
       <c r="K3">
-        <v>8816</v>
+        <v>6142</v>
       </c>
       <c r="L3">
-        <v>0.2183637579570505</v>
+        <v>0.1473467037712312</v>
       </c>
       <c r="M3">
-        <v>5540</v>
+        <v>5097</v>
       </c>
       <c r="N3">
-        <v>0.06653327985050428</v>
+        <v>0.05566835335479101</v>
       </c>
       <c r="O3">
-        <v>0.6284029038112523</v>
+        <v>0.8298599804623901</v>
       </c>
       <c r="P3">
-        <v>1409</v>
+        <v>1375</v>
       </c>
       <c r="Q3">
-        <v>0.01692155077786291</v>
+        <v>0.01501745847809253</v>
       </c>
       <c r="R3">
-        <v>0.1598230490018149</v>
+        <v>0.223868446760013</v>
       </c>
       <c r="S3">
-        <v>4131</v>
+        <v>3722</v>
       </c>
       <c r="T3">
-        <v>0.7456678700361011</v>
+        <v>0.730233470669021</v>
       </c>
       <c r="U3">
-        <v>1620</v>
+        <v>2128</v>
       </c>
       <c r="V3">
-        <v>0.01945558002848681</v>
+        <v>0.0232415648300952</v>
       </c>
       <c r="W3">
-        <v>0.1562760356655381</v>
+        <v>0.1035436123942142</v>
       </c>
       <c r="X3">
-        <v>0.05433302067786813</v>
+        <v>0.0872238263126045</v>
       </c>
       <c r="Y3">
-        <v>0.1019430149876699</v>
+        <v>0.01631978608160974</v>
       </c>
       <c r="Z3">
-        <v>0.6766968311948668</v>
+        <v>0.6760626680878448</v>
       </c>
       <c r="AA3">
-        <v>0.116562044475899</v>
+        <v>0.09493863757176541</v>
       </c>
       <c r="AB3">
-        <v>0.04831953781254059</v>
+        <v>0.07927818805515746</v>
       </c>
       <c r="AC3">
-        <v>0.06824250666335845</v>
+        <v>0.01566044951660794</v>
       </c>
       <c r="AD3">
-        <v>18905</v>
+        <v>19870</v>
       </c>
       <c r="AE3">
-        <v>507.8724055675146</v>
+        <v>441.0060256363095</v>
       </c>
       <c r="AF3">
-        <v>19412.87240556752</v>
+        <v>20311.00602563631</v>
       </c>
       <c r="AG3">
-        <v>17792.87240556752</v>
+        <v>18183.00602563631</v>
       </c>
       <c r="AH3">
-        <v>0.1890628374957924</v>
+        <v>0.1815572112157526</v>
       </c>
       <c r="AI3">
-        <v>0.2465725554972349</v>
+        <v>0.298911026114896</v>
       </c>
       <c r="AJ3">
-        <v>0.1760633811164373</v>
+        <v>0.1656870001600712</v>
       </c>
       <c r="AK3">
-        <v>0.2307440163818306</v>
+        <v>0.2762450907156249</v>
       </c>
       <c r="AL3">
-        <v>492</v>
+        <v>542</v>
       </c>
       <c r="AM3">
-        <v>492</v>
+        <v>542</v>
       </c>
       <c r="AN3">
-        <v>2.278534410027721</v>
+        <v>2.656772295761465</v>
       </c>
       <c r="AO3">
-        <v>15.97154471544715</v>
+        <v>13.01660516605166</v>
       </c>
       <c r="AP3">
-        <v>2.144494685496868</v>
+        <v>2.431208186339926</v>
       </c>
       <c r="AQ3">
-        <v>15.97154471544715</v>
+        <v>13.01660516605166</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0513</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="E2">
-        <v>0.09300000000000001</v>
+        <v>0.0669</v>
       </c>
       <c r="F2">
-        <v>0.141</v>
+        <v>0.145</v>
       </c>
       <c r="G2">
-        <v>0.1958065444774974</v>
+        <v>0.146347528753497</v>
       </c>
       <c r="H2">
-        <v>0.1958065444774974</v>
+        <v>0.146347528753497</v>
       </c>
       <c r="I2">
-        <v>0.1705402263427871</v>
+        <v>0.1888904900998044</v>
       </c>
       <c r="J2">
-        <v>0.1404287532105374</v>
+        <v>0.1552880962012628</v>
       </c>
       <c r="K2">
-        <v>6142</v>
+        <v>7106</v>
       </c>
       <c r="L2">
-        <v>0.1473467037712312</v>
+        <v>0.1472593513625531</v>
       </c>
       <c r="M2">
-        <v>5097</v>
+        <v>3449</v>
       </c>
       <c r="N2">
-        <v>0.05566835335479101</v>
+        <v>0.03740549662331071</v>
       </c>
       <c r="O2">
-        <v>0.8298599804623901</v>
+        <v>0.4853644807205179</v>
       </c>
       <c r="P2">
-        <v>1375</v>
+        <v>1389</v>
       </c>
       <c r="Q2">
-        <v>0.01501745847809253</v>
+        <v>0.01506414462446465</v>
       </c>
       <c r="R2">
-        <v>0.223868446760013</v>
+        <v>0.1954686180692373</v>
       </c>
       <c r="S2">
-        <v>3722</v>
+        <v>2060</v>
       </c>
       <c r="T2">
-        <v>0.730233470669021</v>
+        <v>0.5972745723398086</v>
       </c>
       <c r="U2">
-        <v>2128</v>
+        <v>2586</v>
       </c>
       <c r="V2">
-        <v>0.0232415648300952</v>
+        <v>0.02804598848010481</v>
       </c>
       <c r="W2">
-        <v>0.1035436123942142</v>
+        <v>0.1491635004932933</v>
       </c>
       <c r="X2">
-        <v>0.0872238263126045</v>
+        <v>0.07464731848114881</v>
       </c>
       <c r="Y2">
-        <v>0.01631978608160974</v>
+        <v>0.07451618201214449</v>
       </c>
       <c r="Z2">
-        <v>0.6760626680878448</v>
+        <v>0.9671416941221684</v>
       </c>
       <c r="AA2">
-        <v>0.09493863757176541</v>
+        <v>0.1501855924370956</v>
       </c>
       <c r="AB2">
-        <v>0.07927818805515746</v>
+        <v>0.06901070313049372</v>
       </c>
       <c r="AC2">
-        <v>0.01566044951660794</v>
+        <v>0.0811748893066019</v>
       </c>
       <c r="AD2">
-        <v>19870</v>
+        <v>18830</v>
       </c>
       <c r="AE2">
-        <v>441.0060256363095</v>
+        <v>620.4470011696902</v>
       </c>
       <c r="AF2">
-        <v>20311.00602563631</v>
+        <v>19450.44700116969</v>
       </c>
       <c r="AG2">
-        <v>18183.00602563631</v>
+        <v>16864.44700116969</v>
       </c>
       <c r="AH2">
-        <v>0.1815572112157526</v>
+        <v>0.1741995181059394</v>
       </c>
       <c r="AI2">
-        <v>0.298911026114896</v>
+        <v>0.2527527356654781</v>
       </c>
       <c r="AJ2">
-        <v>0.1656870001600712</v>
+        <v>0.1546201913617008</v>
       </c>
       <c r="AK2">
-        <v>0.2762450907156249</v>
+        <v>0.226768847289556</v>
       </c>
       <c r="AL2">
-        <v>542</v>
+        <v>653</v>
       </c>
       <c r="AM2">
-        <v>542</v>
+        <v>653</v>
       </c>
       <c r="AN2">
-        <v>2.656772295761465</v>
+        <v>1.974001467659084</v>
       </c>
       <c r="AO2">
-        <v>13.01660516605166</v>
+        <v>13.90352220520674</v>
       </c>
       <c r="AP2">
-        <v>2.431208186339926</v>
+        <v>1.767947059562815</v>
       </c>
       <c r="AQ2">
-        <v>13.01660516605166</v>
+        <v>13.90352220520674</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0513</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="E3">
-        <v>0.09300000000000001</v>
+        <v>0.0669</v>
       </c>
       <c r="F3">
-        <v>0.141</v>
+        <v>0.145</v>
       </c>
       <c r="G3">
-        <v>0.1958065444774974</v>
+        <v>0.146347528753497</v>
       </c>
       <c r="H3">
-        <v>0.1958065444774974</v>
+        <v>0.146347528753497</v>
       </c>
       <c r="I3">
-        <v>0.1705402263427871</v>
+        <v>0.1888904900998044</v>
       </c>
       <c r="J3">
-        <v>0.1404287532105374</v>
+        <v>0.1552880962012628</v>
       </c>
       <c r="K3">
-        <v>6142</v>
+        <v>7106</v>
       </c>
       <c r="L3">
-        <v>0.1473467037712312</v>
+        <v>0.1472593513625531</v>
       </c>
       <c r="M3">
-        <v>5097</v>
+        <v>3449</v>
       </c>
       <c r="N3">
-        <v>0.05566835335479101</v>
+        <v>0.03740549662331071</v>
       </c>
       <c r="O3">
-        <v>0.8298599804623901</v>
+        <v>0.4853644807205179</v>
       </c>
       <c r="P3">
-        <v>1375</v>
+        <v>1389</v>
       </c>
       <c r="Q3">
-        <v>0.01501745847809253</v>
+        <v>0.01506414462446465</v>
       </c>
       <c r="R3">
-        <v>0.223868446760013</v>
+        <v>0.1954686180692373</v>
       </c>
       <c r="S3">
-        <v>3722</v>
+        <v>2060</v>
       </c>
       <c r="T3">
-        <v>0.730233470669021</v>
+        <v>0.5972745723398086</v>
       </c>
       <c r="U3">
-        <v>2128</v>
+        <v>2586</v>
       </c>
       <c r="V3">
-        <v>0.0232415648300952</v>
+        <v>0.02804598848010481</v>
       </c>
       <c r="W3">
-        <v>0.1035436123942142</v>
+        <v>0.1491635004932933</v>
       </c>
       <c r="X3">
-        <v>0.0872238263126045</v>
+        <v>0.07464731848114881</v>
       </c>
       <c r="Y3">
-        <v>0.01631978608160974</v>
+        <v>0.07451618201214449</v>
       </c>
       <c r="Z3">
-        <v>0.6760626680878448</v>
+        <v>0.9671416941221684</v>
       </c>
       <c r="AA3">
-        <v>0.09493863757176541</v>
+        <v>0.1501855924370956</v>
       </c>
       <c r="AB3">
-        <v>0.07927818805515746</v>
+        <v>0.06901070313049372</v>
       </c>
       <c r="AC3">
-        <v>0.01566044951660794</v>
+        <v>0.0811748893066019</v>
       </c>
       <c r="AD3">
-        <v>19870</v>
+        <v>18830</v>
       </c>
       <c r="AE3">
-        <v>441.0060256363095</v>
+        <v>620.4470011696902</v>
       </c>
       <c r="AF3">
-        <v>20311.00602563631</v>
+        <v>19450.44700116969</v>
       </c>
       <c r="AG3">
-        <v>18183.00602563631</v>
+        <v>16864.44700116969</v>
       </c>
       <c r="AH3">
-        <v>0.1815572112157526</v>
+        <v>0.1741995181059394</v>
       </c>
       <c r="AI3">
-        <v>0.298911026114896</v>
+        <v>0.2527527356654781</v>
       </c>
       <c r="AJ3">
-        <v>0.1656870001600712</v>
+        <v>0.1546201913617008</v>
       </c>
       <c r="AK3">
-        <v>0.2762450907156249</v>
+        <v>0.226768847289556</v>
       </c>
       <c r="AL3">
-        <v>542</v>
+        <v>653</v>
       </c>
       <c r="AM3">
-        <v>542</v>
+        <v>653</v>
       </c>
       <c r="AN3">
-        <v>2.656772295761465</v>
+        <v>1.974001467659084</v>
       </c>
       <c r="AO3">
-        <v>13.01660516605166</v>
+        <v>13.90352220520674</v>
       </c>
       <c r="AP3">
-        <v>2.431208186339926</v>
+        <v>1.767947059562815</v>
       </c>
       <c r="AQ3">
-        <v>13.01660516605166</v>
+        <v>13.90352220520674</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07820000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="E2">
-        <v>0.0669</v>
+        <v>0.224</v>
       </c>
       <c r="F2">
-        <v>0.145</v>
+        <v>0.0199</v>
       </c>
       <c r="G2">
-        <v>0.146347528753497</v>
+        <v>0.1784010091961168</v>
       </c>
       <c r="H2">
-        <v>0.146347528753497</v>
+        <v>0.1784010091961168</v>
       </c>
       <c r="I2">
-        <v>0.1888904900998044</v>
+        <v>0.2014701399883973</v>
       </c>
       <c r="J2">
-        <v>0.1552880962012628</v>
+        <v>0.1893613208330844</v>
       </c>
       <c r="K2">
-        <v>7106</v>
+        <v>9997</v>
       </c>
       <c r="L2">
-        <v>0.1472593513625531</v>
+        <v>0.182770535861199</v>
       </c>
       <c r="M2">
-        <v>3449</v>
+        <v>3333</v>
       </c>
       <c r="N2">
-        <v>0.03740549662331071</v>
+        <v>0.02992565723315616</v>
       </c>
       <c r="O2">
-        <v>0.4853644807205179</v>
+        <v>0.3334000200060018</v>
       </c>
       <c r="P2">
-        <v>1389</v>
+        <v>1419</v>
       </c>
       <c r="Q2">
-        <v>0.01506414462446465</v>
+        <v>0.01274062634678925</v>
       </c>
       <c r="R2">
-        <v>0.1954686180692373</v>
+        <v>0.1419425827748325</v>
       </c>
       <c r="S2">
-        <v>2060</v>
+        <v>1914</v>
       </c>
       <c r="T2">
-        <v>0.5972745723398086</v>
+        <v>0.5742574257425742</v>
       </c>
       <c r="U2">
-        <v>2586</v>
+        <v>2525</v>
       </c>
       <c r="V2">
-        <v>0.02804598848010481</v>
+        <v>0.02267095244936072</v>
       </c>
       <c r="W2">
-        <v>0.1491635004932933</v>
+        <v>0.190880797357417</v>
       </c>
       <c r="X2">
-        <v>0.07464731848114881</v>
+        <v>0.07931081308141777</v>
       </c>
       <c r="Y2">
-        <v>0.07451618201214449</v>
+        <v>0.1115699842759992</v>
       </c>
       <c r="Z2">
-        <v>0.9671416941221684</v>
+        <v>1.094291513457144</v>
       </c>
       <c r="AA2">
-        <v>0.1501855924370956</v>
+        <v>0.2072164863646798</v>
       </c>
       <c r="AB2">
-        <v>0.06901070313049372</v>
+        <v>0.07380857557298484</v>
       </c>
       <c r="AC2">
-        <v>0.0811748893066019</v>
+        <v>0.133407910791695</v>
       </c>
       <c r="AD2">
-        <v>18830</v>
+        <v>21415</v>
       </c>
       <c r="AE2">
-        <v>620.4470011696902</v>
+        <v>920.9387652731701</v>
       </c>
       <c r="AF2">
-        <v>19450.44700116969</v>
+        <v>22335.93876527317</v>
       </c>
       <c r="AG2">
-        <v>16864.44700116969</v>
+        <v>19810.93876527317</v>
       </c>
       <c r="AH2">
-        <v>0.1741995181059394</v>
+        <v>0.1670452090630678</v>
       </c>
       <c r="AI2">
-        <v>0.2527527356654781</v>
+        <v>0.2415846841594414</v>
       </c>
       <c r="AJ2">
-        <v>0.1546201913617008</v>
+        <v>0.1510130425462552</v>
       </c>
       <c r="AK2">
-        <v>0.226768847289556</v>
+        <v>0.2202905811645232</v>
       </c>
       <c r="AL2">
-        <v>653</v>
+        <v>725</v>
       </c>
       <c r="AM2">
-        <v>653</v>
+        <v>725</v>
       </c>
       <c r="AN2">
-        <v>1.974001467659084</v>
+        <v>1.85748980830948</v>
       </c>
       <c r="AO2">
-        <v>13.90352220520674</v>
+        <v>15.2248275862069</v>
       </c>
       <c r="AP2">
-        <v>1.767947059562815</v>
+        <v>1.71835707912856</v>
       </c>
       <c r="AQ2">
-        <v>13.90352220520674</v>
+        <v>15.2248275862069</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07820000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="E3">
-        <v>0.0669</v>
+        <v>0.224</v>
       </c>
       <c r="F3">
-        <v>0.145</v>
+        <v>0.0199</v>
       </c>
       <c r="G3">
-        <v>0.146347528753497</v>
+        <v>0.1784010091961168</v>
       </c>
       <c r="H3">
-        <v>0.146347528753497</v>
+        <v>0.1784010091961168</v>
       </c>
       <c r="I3">
-        <v>0.1888904900998044</v>
+        <v>0.2014701399883973</v>
       </c>
       <c r="J3">
-        <v>0.1552880962012628</v>
+        <v>0.1893613208330844</v>
       </c>
       <c r="K3">
-        <v>7106</v>
+        <v>9997</v>
       </c>
       <c r="L3">
-        <v>0.1472593513625531</v>
+        <v>0.182770535861199</v>
       </c>
       <c r="M3">
-        <v>3449</v>
+        <v>3333</v>
       </c>
       <c r="N3">
-        <v>0.03740549662331071</v>
+        <v>0.02992565723315616</v>
       </c>
       <c r="O3">
-        <v>0.4853644807205179</v>
+        <v>0.3334000200060018</v>
       </c>
       <c r="P3">
-        <v>1389</v>
+        <v>1419</v>
       </c>
       <c r="Q3">
-        <v>0.01506414462446465</v>
+        <v>0.01274062634678925</v>
       </c>
       <c r="R3">
-        <v>0.1954686180692373</v>
+        <v>0.1419425827748325</v>
       </c>
       <c r="S3">
-        <v>2060</v>
+        <v>1914</v>
       </c>
       <c r="T3">
-        <v>0.5972745723398086</v>
+        <v>0.5742574257425742</v>
       </c>
       <c r="U3">
-        <v>2586</v>
+        <v>2525</v>
       </c>
       <c r="V3">
-        <v>0.02804598848010481</v>
+        <v>0.02267095244936072</v>
       </c>
       <c r="W3">
-        <v>0.1491635004932933</v>
+        <v>0.190880797357417</v>
       </c>
       <c r="X3">
-        <v>0.07464731848114881</v>
+        <v>0.07931081308141777</v>
       </c>
       <c r="Y3">
-        <v>0.07451618201214449</v>
+        <v>0.1115699842759992</v>
       </c>
       <c r="Z3">
-        <v>0.9671416941221684</v>
+        <v>1.094291513457144</v>
       </c>
       <c r="AA3">
-        <v>0.1501855924370956</v>
+        <v>0.2072164863646798</v>
       </c>
       <c r="AB3">
-        <v>0.06901070313049372</v>
+        <v>0.07380857557298484</v>
       </c>
       <c r="AC3">
-        <v>0.0811748893066019</v>
+        <v>0.133407910791695</v>
       </c>
       <c r="AD3">
-        <v>18830</v>
+        <v>21415</v>
       </c>
       <c r="AE3">
-        <v>620.4470011696902</v>
+        <v>920.9387652731701</v>
       </c>
       <c r="AF3">
-        <v>19450.44700116969</v>
+        <v>22335.93876527317</v>
       </c>
       <c r="AG3">
-        <v>16864.44700116969</v>
+        <v>19810.93876527317</v>
       </c>
       <c r="AH3">
-        <v>0.1741995181059394</v>
+        <v>0.1670452090630678</v>
       </c>
       <c r="AI3">
-        <v>0.2527527356654781</v>
+        <v>0.2415846841594414</v>
       </c>
       <c r="AJ3">
-        <v>0.1546201913617008</v>
+        <v>0.1510130425462552</v>
       </c>
       <c r="AK3">
-        <v>0.226768847289556</v>
+        <v>0.2202905811645232</v>
       </c>
       <c r="AL3">
-        <v>653</v>
+        <v>725</v>
       </c>
       <c r="AM3">
-        <v>653</v>
+        <v>725</v>
       </c>
       <c r="AN3">
-        <v>1.974001467659084</v>
+        <v>1.85748980830948</v>
       </c>
       <c r="AO3">
-        <v>13.90352220520674</v>
+        <v>15.2248275862069</v>
       </c>
       <c r="AP3">
-        <v>1.767947059562815</v>
+        <v>1.71835707912856</v>
       </c>
       <c r="AQ3">
-        <v>13.90352220520674</v>
+        <v>15.2248275862069</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_insurance_prop_cas.xlsx
@@ -648,10 +648,10 @@
         <v>0.190880797357417</v>
       </c>
       <c r="X2">
-        <v>0.07931081308141777</v>
+        <v>0.07928926860807059</v>
       </c>
       <c r="Y2">
-        <v>0.1115699842759992</v>
+        <v>0.1115915287493464</v>
       </c>
       <c r="Z2">
         <v>1.094291513457144</v>
@@ -660,10 +660,10 @@
         <v>0.2072164863646798</v>
       </c>
       <c r="AB2">
-        <v>0.07380857557298484</v>
+        <v>0.07379063000069211</v>
       </c>
       <c r="AC2">
-        <v>0.133407910791695</v>
+        <v>0.1334258563639877</v>
       </c>
       <c r="AD2">
         <v>21415</v>
@@ -785,10 +785,10 @@
         <v>0.190880797357417</v>
       </c>
       <c r="X3">
-        <v>0.07931081308141777</v>
+        <v>0.07928926860807059</v>
       </c>
       <c r="Y3">
-        <v>0.1115699842759992</v>
+        <v>0.1115915287493464</v>
       </c>
       <c r="Z3">
         <v>1.094291513457144</v>
@@ -797,10 +797,10 @@
         <v>0.2072164863646798</v>
       </c>
       <c r="AB3">
-        <v>0.07380857557298484</v>
+        <v>0.07379063000069211</v>
       </c>
       <c r="AC3">
-        <v>0.133407910791695</v>
+        <v>0.1334258563639877</v>
       </c>
       <c r="AD3">
         <v>21415</v>
